--- a/Bildvorverarbeitung/Schilderarten.xlsx
+++ b/Bildvorverarbeitung/Schilderarten.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/02520db892aadeb1/Dokumente/GitHub/the-machine-learning-brick/Bildvorverarbeitung/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="11_AD4DB114E441178AC67DF4488651E020683EDF1C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20803760-C4A2-4D90-807A-B6BF1B7F02CE}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="11_AD4DB114E441178AC67DF4488651E020683EDF1C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8A94719-0702-4004-8130-7FA152F4E375}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -189,10 +189,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -507,16 +503,16 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -549,27 +545,28 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>21</v>
       </c>
     </row>
